--- a/data/manual/materials_prices.xlsx
+++ b/data/manual/materials_prices.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sevi\OneDrive - Paul Scherrer Institut\Dateien von Hahn Menacho, Alvaro Jose - Severin's work\3_Code\semesterproject\data\manual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpsich-my.sharepoint.com/personal/alvaro_hahn-menacho_psi_ch/Documents/Severin's work/3_Code/semesterproject/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88AC83D-3D0E-48F6-B25A-3A931C8EAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{D88AC83D-3D0E-48F6-B25A-3A931C8EAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3D7DC24-78F4-4671-BB8B-2374D4921DED}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="0" windowWidth="9750" windowHeight="10155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="292">
   <si>
     <t>material_category</t>
   </si>
@@ -768,6 +768,147 @@
   </si>
   <si>
     <t>manganese</t>
+  </si>
+  <si>
+    <t>nickel-rich materials</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/23952/exchanges</t>
+  </si>
+  <si>
+    <t>silver, unrefined</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/19798/exchanges</t>
+  </si>
+  <si>
+    <t>tin concentrate</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/19388/exchanges</t>
+  </si>
+  <si>
+    <t>platinum group metal concentrate</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/21961/exchanges</t>
+  </si>
+  <si>
+    <t>potash salt</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/22800/exchanges</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/1177/exchanges</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/3653/exchanges</t>
+  </si>
+  <si>
+    <t>sodium phosphate</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/1876/exchanges</t>
+  </si>
+  <si>
+    <t>sodium aluminate, powder</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/11296/exchanges</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/4736/exchanges</t>
+  </si>
+  <si>
+    <t>silver</t>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+  <si>
+    <t>lead</t>
+  </si>
+  <si>
+    <t>platinum</t>
+  </si>
+  <si>
+    <t>palladium</t>
+  </si>
+  <si>
+    <t>cobalt</t>
+  </si>
+  <si>
+    <t>molybdenum</t>
+  </si>
+  <si>
+    <t>niobium</t>
+  </si>
+  <si>
+    <t>antimony</t>
+  </si>
+  <si>
+    <t>rhodium</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/6159/exchanges</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/1779/exchanges</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/6012/exchanges</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/5172/exchanges</t>
+  </si>
+  <si>
+    <t>nickel, class 1</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/7386/exchanges</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/5590/exchanges</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/6223/exchanges</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/9498/exchanges</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/2040/exchanges</t>
+  </si>
+  <si>
+    <t>pig iron</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/20867/exchanges</t>
+  </si>
+  <si>
+    <t>https://www.globemm.com/niobium-markets#:~:text=Currently%2C%20niobium%20prices%20range%20from,specialised%20products%20realise%20higher%20prices.</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/1387/exchanges</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/3889/exchanges</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/22015/exchanges</t>
+  </si>
+  <si>
+    <t>tellurium, semiconductor-grade</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/11094/exchanges</t>
   </si>
 </sst>
 </file>
@@ -799,7 +940,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -809,6 +950,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -826,7 +973,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -837,8 +984,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1145,17 +1297,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H84"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.58984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.76953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.58984375" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1178,7 +1330,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1194,14 +1346,14 @@
       <c r="E2" t="s">
         <v>185</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="6">
         <v>0.84</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1217,14 +1369,14 @@
       <c r="E3" t="s">
         <v>186</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="6">
         <v>9.0700000000000003E-2</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1240,14 +1392,14 @@
       <c r="E4" t="s">
         <v>190</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="6">
         <v>2.9099999999999998E-3</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1263,14 +1415,14 @@
       <c r="E5" t="s">
         <v>191</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="6">
         <v>0.92</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1286,14 +1438,14 @@
       <c r="E6" t="s">
         <v>194</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="6">
         <v>0.88700000000000001</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1310,7 +1462,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1327,7 +1479,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1344,7 +1496,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1360,14 +1512,14 @@
       <c r="E10" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="7">
         <v>5.85</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>4</v>
       </c>
@@ -1383,14 +1535,14 @@
       <c r="E11" t="s">
         <v>201</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="6">
         <v>0.628</v>
       </c>
       <c r="G11" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1398,14 +1550,14 @@
       <c r="E12" t="s">
         <v>199</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="6">
         <v>1.72</v>
       </c>
       <c r="G12" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1422,7 +1574,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1438,14 +1590,14 @@
       <c r="E14" t="s">
         <v>207</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="6">
         <v>8.3800000000000008</v>
       </c>
       <c r="G14" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1461,14 +1613,14 @@
       <c r="E15" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="7">
         <v>3.99</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1484,14 +1636,14 @@
       <c r="E16" t="s">
         <v>211</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="6">
         <v>5.52</v>
       </c>
       <c r="G16" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1507,14 +1659,14 @@
       <c r="E17" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="7">
         <v>5.91E-2</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -1530,14 +1682,14 @@
       <c r="E18" t="s">
         <v>214</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="6">
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G18" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -1554,7 +1706,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1571,7 +1723,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1588,7 +1740,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -1604,14 +1756,14 @@
       <c r="E22" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="7">
         <v>0.21</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -1627,14 +1779,14 @@
       <c r="E23" t="s">
         <v>219</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="6">
         <v>1.6E-2</v>
       </c>
       <c r="G23" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -1650,14 +1802,14 @@
       <c r="E24" t="s">
         <v>224</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="6">
         <v>1.4E-2</v>
       </c>
       <c r="G24" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1673,14 +1825,14 @@
       <c r="E25" t="s">
         <v>227</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="6">
         <v>7.5500000000000003E-3</v>
       </c>
       <c r="G25" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -1696,14 +1848,14 @@
       <c r="E26" t="s">
         <v>220</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="6">
         <v>0.13</v>
       </c>
       <c r="G26" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1719,14 +1871,14 @@
       <c r="E27" t="s">
         <v>218</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="6">
         <v>0.21</v>
       </c>
       <c r="G27" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -1743,7 +1895,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
@@ -1759,14 +1911,14 @@
       <c r="E29" t="s">
         <v>230</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="6">
         <v>0.04</v>
       </c>
       <c r="G29" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -1774,14 +1926,14 @@
       <c r="E30" t="s">
         <v>231</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="6">
         <v>4.53E-2</v>
       </c>
       <c r="G30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -1797,14 +1949,14 @@
       <c r="E31" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="7">
         <v>0.84</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -1820,14 +1972,14 @@
       <c r="E32" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="8">
         <v>21400</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -1844,7 +1996,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -1860,14 +2012,14 @@
       <c r="E34" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="7">
         <v>0.84</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1880,17 +2032,17 @@
       <c r="D35" t="s">
         <v>75</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" t="s">
         <v>221</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="6">
         <v>3.78E-2</v>
       </c>
       <c r="G35" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -1906,14 +2058,14 @@
       <c r="E36" t="s">
         <v>238</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="6">
         <v>0.17599999999999999</v>
       </c>
       <c r="G36" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1929,14 +2081,14 @@
       <c r="E37" t="s">
         <v>240</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="6">
         <v>0.84599999999999997</v>
       </c>
       <c r="G37" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -1952,14 +2104,14 @@
       <c r="E38" t="s">
         <v>222</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="6">
         <v>1.1499999999999999</v>
       </c>
       <c r="G38" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -1975,14 +2127,14 @@
       <c r="E39" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="7">
         <v>1.24</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -1995,8 +2147,17 @@
       <c r="D40" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="E40" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F40" s="7">
+        <v>11.2</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>38</v>
       </c>
@@ -2009,8 +2170,17 @@
       <c r="D41" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="E41" t="s">
+        <v>247</v>
+      </c>
+      <c r="F41" s="6">
+        <v>432</v>
+      </c>
+      <c r="G41" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>38</v>
       </c>
@@ -2023,8 +2193,11 @@
       <c r="D42" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H42" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -2037,8 +2210,17 @@
       <c r="D43" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="E43" t="s">
+        <v>249</v>
+      </c>
+      <c r="F43" s="6">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G43" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -2054,14 +2236,14 @@
       <c r="E44" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="7">
         <v>5.85</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -2074,8 +2256,17 @@
       <c r="D45" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="E45" t="s">
+        <v>194</v>
+      </c>
+      <c r="F45" s="6">
+        <v>0.88700000000000001</v>
+      </c>
+      <c r="G45" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -2088,8 +2279,11 @@
       <c r="D46" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H46" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>38</v>
       </c>
@@ -2102,8 +2296,17 @@
       <c r="D47" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="E47" t="s">
+        <v>251</v>
+      </c>
+      <c r="F47" s="9">
+        <v>1360</v>
+      </c>
+      <c r="G47" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>38</v>
       </c>
@@ -2116,8 +2319,11 @@
       <c r="D48" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="H48" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>38</v>
       </c>
@@ -2130,8 +2336,17 @@
       <c r="D49" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E49" t="s">
+        <v>253</v>
+      </c>
+      <c r="F49" s="6">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="G49" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -2144,8 +2359,17 @@
       <c r="D50" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E50" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F50" s="7">
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2158,8 +2382,17 @@
       <c r="D51" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E51" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F51" s="7">
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>104</v>
       </c>
@@ -2172,8 +2405,17 @@
       <c r="D52" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E52" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F52" s="7">
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -2186,8 +2428,17 @@
       <c r="D53" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E53" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F53" s="7">
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -2200,8 +2451,17 @@
       <c r="D54" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E54" t="s">
+        <v>257</v>
+      </c>
+      <c r="F54" s="6">
+        <v>4.0099999999999997E-2</v>
+      </c>
+      <c r="G54" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -2214,8 +2474,17 @@
       <c r="D55" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E55" t="s">
+        <v>255</v>
+      </c>
+      <c r="F55" s="6">
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="G55" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>118</v>
       </c>
@@ -2228,8 +2497,17 @@
       <c r="D56" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E56" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F56" s="7">
+        <v>0.99</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>118</v>
       </c>
@@ -2242,8 +2520,17 @@
       <c r="D57" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E57" t="s">
+        <v>261</v>
+      </c>
+      <c r="F57" s="6">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="G57" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>118</v>
       </c>
@@ -2257,7 +2544,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>118</v>
       </c>
@@ -2270,8 +2557,17 @@
       <c r="D59" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E59" t="s">
+        <v>207</v>
+      </c>
+      <c r="F59" s="6">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="G59" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>118</v>
       </c>
@@ -2287,14 +2583,14 @@
       <c r="E60" t="s">
         <v>203</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="6">
         <v>2.36</v>
       </c>
       <c r="G60" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2302,14 +2598,14 @@
       <c r="E61" t="s">
         <v>205</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="6">
         <v>22.5</v>
       </c>
       <c r="G61" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -2322,8 +2618,17 @@
       <c r="D62" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E62" t="s">
+        <v>264</v>
+      </c>
+      <c r="F62" s="6">
+        <v>445</v>
+      </c>
+      <c r="G62" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>118</v>
       </c>
@@ -2336,8 +2641,17 @@
       <c r="D63" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E63" t="s">
+        <v>265</v>
+      </c>
+      <c r="F63" s="9">
+        <v>35300</v>
+      </c>
+      <c r="G63" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>118</v>
       </c>
@@ -2350,8 +2664,17 @@
       <c r="D64" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E64" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F64" s="7">
+        <v>5.52</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>118</v>
       </c>
@@ -2364,8 +2687,17 @@
       <c r="D65" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E65" t="s">
+        <v>194</v>
+      </c>
+      <c r="F65" s="6">
+        <v>2.13</v>
+      </c>
+      <c r="G65" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -2378,8 +2710,17 @@
       <c r="D66" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E66" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F66" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>118</v>
       </c>
@@ -2392,8 +2733,17 @@
       <c r="D67" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E67" t="s">
+        <v>266</v>
+      </c>
+      <c r="F67" s="6">
+        <v>1.64</v>
+      </c>
+      <c r="G67" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>118</v>
       </c>
@@ -2406,8 +2756,17 @@
       <c r="D68" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E68" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="F68" s="9">
+        <v>24900</v>
+      </c>
+      <c r="G68" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>118</v>
       </c>
@@ -2420,8 +2779,17 @@
       <c r="D69" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E69" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F69" s="9">
+        <v>28100</v>
+      </c>
+      <c r="G69" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>118</v>
       </c>
@@ -2434,8 +2802,17 @@
       <c r="D70" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E70" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="F70" s="6">
+        <v>32.1</v>
+      </c>
+      <c r="G70" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>118</v>
       </c>
@@ -2448,8 +2825,17 @@
       <c r="D71" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E71" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F71" s="6">
+        <v>27</v>
+      </c>
+      <c r="G71" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>118</v>
       </c>
@@ -2462,8 +2848,17 @@
       <c r="D72" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E72" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F72" s="6">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="G72" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>118</v>
       </c>
@@ -2476,8 +2871,17 @@
       <c r="D73" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E73" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="F73" s="6">
+        <v>1.24</v>
+      </c>
+      <c r="G73" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>118</v>
       </c>
@@ -2490,8 +2894,17 @@
       <c r="D74" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E74" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="F74" s="12">
+        <v>45</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2504,8 +2917,17 @@
       <c r="D75" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E75" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F75" s="6">
+        <v>16.7</v>
+      </c>
+      <c r="G75" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>118</v>
       </c>
@@ -2518,8 +2940,17 @@
       <c r="D76" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E76" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F76" s="6">
+        <v>5.62</v>
+      </c>
+      <c r="G76" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>118</v>
       </c>
@@ -2532,8 +2963,17 @@
       <c r="D77" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E77" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F77" s="9">
+        <v>118000</v>
+      </c>
+      <c r="G77" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>118</v>
       </c>
@@ -2546,8 +2986,11 @@
       <c r="D78" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="G78" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>118</v>
       </c>
@@ -2560,8 +3003,11 @@
       <c r="D79" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="G79" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>118</v>
       </c>
@@ -2574,8 +3020,17 @@
       <c r="D80" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="E80" t="s">
+        <v>290</v>
+      </c>
+      <c r="F80" s="6">
+        <v>49.5</v>
+      </c>
+      <c r="G80" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>169</v>
       </c>
@@ -2588,8 +3043,11 @@
       <c r="D81" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="G81" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>169</v>
       </c>
@@ -2602,8 +3060,11 @@
       <c r="D82" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="G82" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>169</v>
       </c>
@@ -2616,8 +3077,11 @@
       <c r="D83" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="G83" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>169</v>
       </c>
@@ -2629,6 +3093,15 @@
       </c>
       <c r="D84" t="s">
         <v>181</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F84" s="7">
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual/materials_prices.xlsx
+++ b/data/manual/materials_prices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpsich-my.sharepoint.com/personal/alvaro_hahn-menacho_psi_ch/Documents/Severin's work/3_Code/semesterproject/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{D88AC83D-3D0E-48F6-B25A-3A931C8EAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3D7DC24-78F4-4671-BB8B-2374D4921DED}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{D88AC83D-3D0E-48F6-B25A-3A931C8EAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31949691-E44D-420F-BA4F-560A928C2BB4}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="294">
   <si>
     <t>material_category</t>
   </si>
@@ -909,6 +909,12 @@
   </si>
   <si>
     <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/11094/exchanges</t>
+  </si>
+  <si>
+    <t>molybdenite</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/2695/exchanges</t>
   </si>
 </sst>
 </file>
@@ -973,7 +979,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -981,16 +987,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1304,7 +1307,7 @@
     <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1346,7 +1349,7 @@
       <c r="E2" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2">
         <v>0.84</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -1369,7 +1372,7 @@
       <c r="E3" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3">
         <v>9.0700000000000003E-2</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -1392,7 +1395,7 @@
       <c r="E4" t="s">
         <v>190</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4">
         <v>2.9099999999999998E-3</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -1415,7 +1418,7 @@
       <c r="E5" t="s">
         <v>191</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5">
         <v>0.92</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -1438,7 +1441,7 @@
       <c r="E6" t="s">
         <v>194</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6">
         <v>0.88700000000000001</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -1458,8 +1461,14 @@
       <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="H7" t="s">
-        <v>195</v>
+      <c r="E7" t="s">
+        <v>292</v>
+      </c>
+      <c r="F7">
+        <v>5.84</v>
+      </c>
+      <c r="G7" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1492,8 +1501,14 @@
       <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="H9" t="s">
-        <v>195</v>
+      <c r="E9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F9">
+        <v>2.9099999999999998E-3</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1512,7 +1527,7 @@
       <c r="E10" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="3">
         <v>5.85</v>
       </c>
       <c r="G10" s="4" t="s">
@@ -1520,22 +1535,22 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E11" t="s">
         <v>201</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11">
         <v>0.628</v>
       </c>
       <c r="G11" t="s">
@@ -1543,14 +1558,14 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
       <c r="E12" t="s">
         <v>199</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12">
         <v>1.72</v>
       </c>
       <c r="G12" t="s">
@@ -1590,7 +1605,7 @@
       <c r="E14" t="s">
         <v>207</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14">
         <v>8.3800000000000008</v>
       </c>
       <c r="G14" t="s">
@@ -1613,7 +1628,7 @@
       <c r="E15" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="3">
         <v>3.99</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -1636,7 +1651,7 @@
       <c r="E16" t="s">
         <v>211</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16">
         <v>5.52</v>
       </c>
       <c r="G16" t="s">
@@ -1659,7 +1674,7 @@
       <c r="E17" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="3">
         <v>5.91E-2</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -1682,7 +1697,7 @@
       <c r="E18" t="s">
         <v>214</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18">
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G18" t="s">
@@ -1756,7 +1771,7 @@
       <c r="E22" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="3">
         <v>0.21</v>
       </c>
       <c r="G22" s="3" t="s">
@@ -1779,7 +1794,7 @@
       <c r="E23" t="s">
         <v>219</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23">
         <v>1.6E-2</v>
       </c>
       <c r="G23" t="s">
@@ -1802,7 +1817,7 @@
       <c r="E24" t="s">
         <v>224</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24">
         <v>1.4E-2</v>
       </c>
       <c r="G24" t="s">
@@ -1825,7 +1840,7 @@
       <c r="E25" t="s">
         <v>227</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25">
         <v>7.5500000000000003E-3</v>
       </c>
       <c r="G25" t="s">
@@ -1848,7 +1863,7 @@
       <c r="E26" t="s">
         <v>220</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26">
         <v>0.13</v>
       </c>
       <c r="G26" t="s">
@@ -1871,7 +1886,7 @@
       <c r="E27" t="s">
         <v>218</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27">
         <v>0.21</v>
       </c>
       <c r="G27" t="s">
@@ -1896,22 +1911,22 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E29" t="s">
         <v>230</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29">
         <v>0.04</v>
       </c>
       <c r="G29" t="s">
@@ -1919,14 +1934,14 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
       <c r="E30" t="s">
         <v>231</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30">
         <v>4.53E-2</v>
       </c>
       <c r="G30" t="s">
@@ -1949,7 +1964,7 @@
       <c r="E31" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="3">
         <v>0.84</v>
       </c>
       <c r="G31" s="3" t="s">
@@ -1972,7 +1987,7 @@
       <c r="E32" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="5">
         <v>21400</v>
       </c>
       <c r="G32" s="3" t="s">
@@ -2012,7 +2027,7 @@
       <c r="E34" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="3">
         <v>0.84</v>
       </c>
       <c r="G34" s="3" t="s">
@@ -2035,7 +2050,7 @@
       <c r="E35" t="s">
         <v>221</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35">
         <v>3.78E-2</v>
       </c>
       <c r="G35" t="s">
@@ -2058,7 +2073,7 @@
       <c r="E36" t="s">
         <v>238</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36">
         <v>0.17599999999999999</v>
       </c>
       <c r="G36" t="s">
@@ -2081,7 +2096,7 @@
       <c r="E37" t="s">
         <v>240</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37">
         <v>0.84599999999999997</v>
       </c>
       <c r="G37" t="s">
@@ -2104,7 +2119,7 @@
       <c r="E38" t="s">
         <v>222</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38">
         <v>1.1499999999999999</v>
       </c>
       <c r="G38" t="s">
@@ -2127,7 +2142,7 @@
       <c r="E39" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="3">
         <v>1.24</v>
       </c>
       <c r="G39" s="3" t="s">
@@ -2150,7 +2165,7 @@
       <c r="E40" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="3">
         <v>11.2</v>
       </c>
       <c r="G40" s="3" t="s">
@@ -2173,7 +2188,7 @@
       <c r="E41" t="s">
         <v>247</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41">
         <v>432</v>
       </c>
       <c r="G41" t="s">
@@ -2213,7 +2228,7 @@
       <c r="E43" t="s">
         <v>249</v>
       </c>
-      <c r="F43" s="6">
+      <c r="F43">
         <v>9.3000000000000007</v>
       </c>
       <c r="G43" t="s">
@@ -2236,7 +2251,7 @@
       <c r="E44" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="3">
         <v>5.85</v>
       </c>
       <c r="G44" s="4" t="s">
@@ -2259,7 +2274,7 @@
       <c r="E45" t="s">
         <v>194</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F45">
         <v>0.88700000000000001</v>
       </c>
       <c r="G45" t="s">
@@ -2299,7 +2314,7 @@
       <c r="E47" t="s">
         <v>251</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="6">
         <v>1360</v>
       </c>
       <c r="G47" t="s">
@@ -2339,7 +2354,7 @@
       <c r="E49" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F49">
         <v>1.1299999999999999E-2</v>
       </c>
       <c r="G49" t="s">
@@ -2362,7 +2377,7 @@
       <c r="E50" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F50" s="3">
         <v>8.6900000000000005E-2</v>
       </c>
       <c r="G50" s="3" t="s">
@@ -2385,7 +2400,7 @@
       <c r="E51" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51" s="3">
         <v>8.6900000000000005E-2</v>
       </c>
       <c r="G51" s="3" t="s">
@@ -2408,7 +2423,7 @@
       <c r="E52" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52" s="3">
         <v>8.6900000000000005E-2</v>
       </c>
       <c r="G52" s="3" t="s">
@@ -2431,7 +2446,7 @@
       <c r="E53" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F53" s="3">
         <v>8.6900000000000005E-2</v>
       </c>
       <c r="G53" s="3" t="s">
@@ -2454,7 +2469,7 @@
       <c r="E54" t="s">
         <v>257</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54">
         <v>4.0099999999999997E-2</v>
       </c>
       <c r="G54" t="s">
@@ -2477,7 +2492,7 @@
       <c r="E55" t="s">
         <v>255</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F55">
         <v>8.6900000000000005E-2</v>
       </c>
       <c r="G55" t="s">
@@ -2500,7 +2515,7 @@
       <c r="E56" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56" s="3">
         <v>0.99</v>
       </c>
       <c r="G56" s="3" t="s">
@@ -2523,7 +2538,7 @@
       <c r="E57" t="s">
         <v>261</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F57">
         <v>0.88100000000000001</v>
       </c>
       <c r="G57" t="s">
@@ -2560,7 +2575,7 @@
       <c r="E59" t="s">
         <v>207</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59">
         <v>8.3800000000000008</v>
       </c>
       <c r="G59" t="s">
@@ -2568,22 +2583,22 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" s="8" t="s">
         <v>129</v>
       </c>
       <c r="E60" t="s">
         <v>203</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F60">
         <v>2.36</v>
       </c>
       <c r="G60" t="s">
@@ -2591,14 +2606,14 @@
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
+      <c r="A61" s="8"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
       <c r="E61" t="s">
         <v>205</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F61">
         <v>22.5</v>
       </c>
       <c r="G61" t="s">
@@ -2621,7 +2636,7 @@
       <c r="E62" t="s">
         <v>264</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F62">
         <v>445</v>
       </c>
       <c r="G62" t="s">
@@ -2644,7 +2659,7 @@
       <c r="E63" t="s">
         <v>265</v>
       </c>
-      <c r="F63" s="9">
+      <c r="F63" s="6">
         <v>35300</v>
       </c>
       <c r="G63" t="s">
@@ -2667,7 +2682,7 @@
       <c r="E64" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F64" s="3">
         <v>5.52</v>
       </c>
       <c r="G64" s="3" t="s">
@@ -2690,7 +2705,7 @@
       <c r="E65" t="s">
         <v>194</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65">
         <v>2.13</v>
       </c>
       <c r="G65" t="s">
@@ -2713,7 +2728,7 @@
       <c r="E66" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66" s="3">
         <v>12.5</v>
       </c>
       <c r="G66" s="3" t="s">
@@ -2736,7 +2751,7 @@
       <c r="E67" t="s">
         <v>266</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F67">
         <v>1.64</v>
       </c>
       <c r="G67" t="s">
@@ -2756,10 +2771,10 @@
       <c r="D68" t="s">
         <v>144</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E68" t="s">
         <v>267</v>
       </c>
-      <c r="F68" s="9">
+      <c r="F68" s="6">
         <v>24900</v>
       </c>
       <c r="G68" t="s">
@@ -2779,10 +2794,10 @@
       <c r="D69" t="s">
         <v>146</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" t="s">
         <v>268</v>
       </c>
-      <c r="F69" s="9">
+      <c r="F69" s="6">
         <v>28100</v>
       </c>
       <c r="G69" t="s">
@@ -2802,10 +2817,10 @@
       <c r="D70" t="s">
         <v>148</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="E70" t="s">
         <v>269</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70">
         <v>32.1</v>
       </c>
       <c r="G70" t="s">
@@ -2825,10 +2840,10 @@
       <c r="D71" t="s">
         <v>150</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" t="s">
         <v>270</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71">
         <v>27</v>
       </c>
       <c r="G71" t="s">
@@ -2848,10 +2863,10 @@
       <c r="D72" t="s">
         <v>152</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="E72" t="s">
         <v>284</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72">
         <v>0.29399999999999998</v>
       </c>
       <c r="G72" t="s">
@@ -2871,10 +2886,10 @@
       <c r="D73" t="s">
         <v>154</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" t="s">
         <v>244</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F73">
         <v>1.24</v>
       </c>
       <c r="G73" t="s">
@@ -2894,13 +2909,13 @@
       <c r="D74" t="s">
         <v>156</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="F74" s="12">
+      <c r="F74" s="7">
         <v>45</v>
       </c>
-      <c r="G74" s="11" t="s">
+      <c r="G74" s="9" t="s">
         <v>286</v>
       </c>
     </row>
@@ -2917,10 +2932,10 @@
       <c r="D75" t="s">
         <v>158</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" t="s">
         <v>249</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F75">
         <v>16.7</v>
       </c>
       <c r="G75" t="s">
@@ -2940,10 +2955,10 @@
       <c r="D76" t="s">
         <v>160</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E76" t="s">
         <v>272</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F76">
         <v>5.62</v>
       </c>
       <c r="G76" t="s">
@@ -2963,10 +2978,10 @@
       <c r="D77" t="s">
         <v>162</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" t="s">
         <v>273</v>
       </c>
-      <c r="F77" s="9">
+      <c r="F77" s="6">
         <v>118000</v>
       </c>
       <c r="G77" t="s">
@@ -2986,7 +3001,7 @@
       <c r="D78" t="s">
         <v>164</v>
       </c>
-      <c r="G78" s="6" t="s">
+      <c r="G78" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3003,7 +3018,7 @@
       <c r="D79" t="s">
         <v>166</v>
       </c>
-      <c r="G79" s="6" t="s">
+      <c r="G79" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3023,7 +3038,7 @@
       <c r="E80" t="s">
         <v>290</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F80">
         <v>49.5</v>
       </c>
       <c r="G80" t="s">
@@ -3043,7 +3058,7 @@
       <c r="D81" t="s">
         <v>172</v>
       </c>
-      <c r="G81" s="6" t="s">
+      <c r="G81" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3060,7 +3075,7 @@
       <c r="D82" t="s">
         <v>175</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="G82" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3077,7 +3092,7 @@
       <c r="D83" t="s">
         <v>178</v>
       </c>
-      <c r="G83" s="6" t="s">
+      <c r="G83" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3097,7 +3112,7 @@
       <c r="E84" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F84" s="7">
+      <c r="F84" s="3">
         <v>8.6900000000000005E-2</v>
       </c>
       <c r="G84" s="3" t="s">
@@ -3127,6 +3142,8 @@
     <hyperlink ref="G6" r:id="rId5" xr:uid="{80AC76BE-D6C1-494A-B6A4-50B84FF949CA}"/>
     <hyperlink ref="G10" r:id="rId6" xr:uid="{4DD938DE-8948-47A8-8630-85DF0C972A5C}"/>
     <hyperlink ref="G44" r:id="rId7" xr:uid="{523F7310-806C-481A-85FF-51B7F8B8EAAB}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{FBACBB21-1F5D-43E9-901F-3651F9F72D65}"/>
+    <hyperlink ref="G74" r:id="rId9" location=":~:text=Currently%2C%20niobium%20prices%20range%20from,specialised%20products%20realise%20higher%20prices." xr:uid="{611CE029-EF7F-449F-AF7D-ADEC470297CE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/manual/materials_prices.xlsx
+++ b/data/manual/materials_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpsich-my.sharepoint.com/personal/alvaro_hahn-menacho_psi_ch/Documents/Severin's work/3_Code/semesterproject/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{D88AC83D-3D0E-48F6-B25A-3A931C8EAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31949691-E44D-420F-BA4F-560A928C2BB4}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="13_ncr:1_{D88AC83D-3D0E-48F6-B25A-3A931C8EAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEFF2073-927D-408B-B424-8FF6646D1DC0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="297">
   <si>
     <t>material_category</t>
   </si>
@@ -915,6 +915,15 @@
   </si>
   <si>
     <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/2695/exchanges</t>
+  </si>
+  <si>
+    <t>https://github.com/polca/premise/blob/master/premise/data/additional_inventories/lci-PGM.xlsx</t>
+  </si>
+  <si>
+    <t>conversion factor dollar -&gt; Euro = 0.86</t>
+  </si>
+  <si>
+    <t>Average of platinum, palladium, rhodium, ruthenium, iridium</t>
   </si>
 </sst>
 </file>
@@ -961,7 +970,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -979,7 +988,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -990,10 +999,11 @@
     <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1299,7 +1309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
@@ -1535,16 +1545,16 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="10" t="s">
         <v>25</v>
       </c>
       <c r="E11" t="s">
@@ -1558,10 +1568,10 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
       <c r="E12" t="s">
         <v>199</v>
       </c>
@@ -1911,16 +1921,16 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="10" t="s">
         <v>65</v>
       </c>
       <c r="E29" t="s">
@@ -1934,10 +1944,10 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
       <c r="E30" t="s">
         <v>231</v>
       </c>
@@ -2583,16 +2593,16 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="10" t="s">
         <v>129</v>
       </c>
       <c r="E60" t="s">
@@ -2606,10 +2616,10 @@
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
       <c r="E61" t="s">
         <v>205</v>
       </c>
@@ -2689,7 +2699,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>118</v>
       </c>
@@ -2712,7 +2722,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -2735,7 +2745,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>118</v>
       </c>
@@ -2758,7 +2768,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>118</v>
       </c>
@@ -2781,7 +2791,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>118</v>
       </c>
@@ -2804,7 +2814,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>118</v>
       </c>
@@ -2827,7 +2837,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>118</v>
       </c>
@@ -2850,7 +2860,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>118</v>
       </c>
@@ -2873,7 +2883,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>118</v>
       </c>
@@ -2896,7 +2906,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>118</v>
       </c>
@@ -2919,7 +2929,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2942,7 +2952,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>118</v>
       </c>
@@ -2965,7 +2975,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>118</v>
       </c>
@@ -2988,7 +2998,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>118</v>
       </c>
@@ -3001,11 +3011,21 @@
       <c r="D78" t="s">
         <v>164</v>
       </c>
-      <c r="G78" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E78" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F78" s="7">
+        <f>107000*0.86</f>
+        <v>92020</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>118</v>
       </c>
@@ -3018,11 +3038,21 @@
       <c r="D79" t="s">
         <v>166</v>
       </c>
-      <c r="G79" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E79" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F79" s="7">
+        <f>10300*0.86</f>
+        <v>8858</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>118</v>
       </c>
@@ -3092,8 +3122,15 @@
       <c r="D83" t="s">
         <v>178</v>
       </c>
-      <c r="G83" t="s">
-        <v>195</v>
+      <c r="E83" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F83" s="8">
+        <f>AVERAGE(F78:F79,F68:F69,F77)</f>
+        <v>54375.6</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/manual/materials_prices.xlsx
+++ b/data/manual/materials_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpsich-my.sharepoint.com/personal/alvaro_hahn-menacho_psi_ch/Documents/Severin's work/3_Code/semesterproject/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="157" documentId="13_ncr:1_{D88AC83D-3D0E-48F6-B25A-3A931C8EAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEFF2073-927D-408B-B424-8FF6646D1DC0}"/>
+  <xr:revisionPtr revIDLastSave="190" documentId="13_ncr:1_{D88AC83D-3D0E-48F6-B25A-3A931C8EAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BE5B1C7-5415-467C-BCA0-27A3ABC7A18A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="302">
   <si>
     <t>material_category</t>
   </si>
@@ -924,6 +924,21 @@
   </si>
   <si>
     <t>Average of platinum, palladium, rhodium, ruthenium, iridium</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/commodity/uranium</t>
+  </si>
+  <si>
+    <t>76.1 USD/Lbs</t>
+  </si>
+  <si>
+    <t>https://www.pricescope.com/diamond-prices/diamond-prices-chart/</t>
+  </si>
+  <si>
+    <t>Sodium Bicarbonate</t>
+  </si>
+  <si>
+    <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/19124/exchanges</t>
   </si>
 </sst>
 </file>
@@ -988,7 +1003,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1004,6 +1019,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1309,18 +1327,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q84"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q87"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1343,7 +1361,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1366,7 +1384,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1389,7 +1407,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1412,7 +1430,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1435,7 +1453,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1458,7 +1476,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1481,7 +1499,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1498,7 +1516,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1521,7 +1539,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1544,62 +1562,53 @@
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A11" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="12"/>
+      <c r="F11" s="12">
+        <f>AVERAGE(F12:F13)</f>
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="G11" s="13"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="E12" t="s">
         <v>201</v>
       </c>
-      <c r="F11">
+      <c r="F12">
         <v>0.628</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G12" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" t="s">
         <v>199</v>
       </c>
-      <c r="F12">
+      <c r="F13">
         <v>1.72</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G13" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1607,45 +1616,39 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" t="s">
-        <v>207</v>
-      </c>
-      <c r="F14">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="G14" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="H14" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3.99</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F15">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="G15" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1653,68 +1656,68 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" t="s">
-        <v>211</v>
-      </c>
-      <c r="F16">
-        <v>5.52</v>
-      </c>
-      <c r="G16" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F16" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>4</v>
       </c>
       <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" t="s">
+        <v>211</v>
+      </c>
+      <c r="F17">
+        <v>5.52</v>
+      </c>
+      <c r="G17" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
         <v>35</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>36</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F18" s="3">
         <v>5.91E-2</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" t="s">
-        <v>214</v>
-      </c>
-      <c r="F18">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="G18" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -1722,16 +1725,22 @@
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
+        <v>214</v>
+      </c>
+      <c r="F19">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G19" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1739,16 +1748,16 @@
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H20" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1756,16 +1765,16 @@
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H21" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -1773,45 +1782,39 @@
         <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0.21</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="H22" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" t="s">
-        <v>219</v>
-      </c>
-      <c r="F23">
-        <v>1.6E-2</v>
-      </c>
-      <c r="G23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -1819,22 +1822,22 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E24" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F24">
-        <v>1.4E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G24" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1842,22 +1845,22 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E25" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F25">
-        <v>7.5500000000000003E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -1865,22 +1868,22 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E26" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F26">
-        <v>0.13</v>
+        <v>7.5500000000000003E-3</v>
       </c>
       <c r="G26" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1888,123 +1891,106 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E27" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F27">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="G27" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>38</v>
       </c>
       <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" t="s">
+        <v>218</v>
+      </c>
+      <c r="F28">
+        <v>0.21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" t="s">
         <v>61</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
         <v>62</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>63</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H29" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A30" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B30" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C30" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D30" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F30">
+        <f>AVERAGE(F31:F32)</f>
+        <v>4.265E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="E31" t="s">
         <v>230</v>
       </c>
-      <c r="F29">
+      <c r="F31">
         <v>0.04</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G31" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" t="s">
         <v>231</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <v>4.53E-2</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G32" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" t="s">
-        <v>67</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F31" s="3">
-        <v>0.84</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" t="s">
-        <v>69</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F32" s="5">
-        <v>21400</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -2012,16 +1998,22 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D33" t="s">
-        <v>71</v>
-      </c>
-      <c r="H33" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -2029,22 +2021,22 @@
         <v>61</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F34" s="3">
-        <v>0.84</v>
+        <v>235</v>
+      </c>
+      <c r="F34" s="5">
+        <v>21400</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -2052,22 +2044,16 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
-        <v>75</v>
-      </c>
-      <c r="E35" t="s">
-        <v>221</v>
-      </c>
-      <c r="F35">
-        <v>3.78E-2</v>
-      </c>
-      <c r="G35" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="H35" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -2075,22 +2061,22 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D36" t="s">
-        <v>77</v>
-      </c>
-      <c r="E36" t="s">
-        <v>238</v>
-      </c>
-      <c r="F36">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="G36" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -2098,22 +2084,22 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E37" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="F37">
-        <v>0.84599999999999997</v>
+        <v>3.78E-2</v>
       </c>
       <c r="G37" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2121,22 +2107,22 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E38" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="F38">
-        <v>1.1499999999999999</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="G38" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -2144,22 +2130,22 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>83</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="F39" s="3">
-        <v>1.24</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="E39" t="s">
+        <v>240</v>
+      </c>
+      <c r="F39">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="G39" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -2167,22 +2153,22 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>85</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F40" s="3">
-        <v>11.2</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="E40" t="s">
+        <v>222</v>
+      </c>
+      <c r="F40">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G40" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>38</v>
       </c>
@@ -2190,22 +2176,22 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D41" t="s">
-        <v>87</v>
-      </c>
-      <c r="E41" t="s">
-        <v>247</v>
-      </c>
-      <c r="F41">
-        <v>432</v>
-      </c>
-      <c r="G41" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>38</v>
       </c>
@@ -2213,16 +2199,22 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
-      </c>
-      <c r="H42" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F42" s="3">
+        <v>11.2</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -2230,22 +2222,22 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D43" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E43" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F43">
-        <v>9.3000000000000007</v>
+        <v>432</v>
       </c>
       <c r="G43" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -2253,22 +2245,16 @@
         <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
-        <v>93</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F44" s="3">
-        <v>5.85</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="H44" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -2276,22 +2262,22 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D45" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E45" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="F45">
-        <v>0.88700000000000001</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="G45" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -2299,16 +2285,22 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
-      </c>
-      <c r="H46" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F46" s="3">
+        <v>5.85</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>38</v>
       </c>
@@ -2316,22 +2308,22 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E47" t="s">
-        <v>251</v>
-      </c>
-      <c r="F47" s="6">
-        <v>1360</v>
+        <v>194</v>
+      </c>
+      <c r="F47">
+        <v>0.88700000000000001</v>
       </c>
       <c r="G47" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>38</v>
       </c>
@@ -2339,16 +2331,16 @@
         <v>61</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D48" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H48" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>38</v>
       </c>
@@ -2356,68 +2348,62 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49" t="s">
+        <v>251</v>
+      </c>
+      <c r="F49" s="6">
+        <v>1360</v>
+      </c>
+      <c r="G49" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A50" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" t="s">
+        <v>101</v>
+      </c>
+      <c r="H50" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A51" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" t="s">
         <v>102</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D51" t="s">
         <v>103</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E51" t="s">
         <v>253</v>
       </c>
-      <c r="F49">
+      <c r="F51">
         <v>1.1299999999999999E-2</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G51" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>104</v>
-      </c>
-      <c r="B50" t="s">
-        <v>105</v>
-      </c>
-      <c r="C50" t="s">
-        <v>106</v>
-      </c>
-      <c r="D50" t="s">
-        <v>107</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F50" s="3">
-        <v>8.6900000000000005E-2</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>104</v>
-      </c>
-      <c r="B51" t="s">
-        <v>105</v>
-      </c>
-      <c r="C51" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" t="s">
-        <v>109</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F51" s="3">
-        <v>8.6900000000000005E-2</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>104</v>
       </c>
@@ -2425,10 +2411,10 @@
         <v>105</v>
       </c>
       <c r="C52" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D52" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>255</v>
@@ -2440,7 +2426,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -2448,10 +2434,10 @@
         <v>105</v>
       </c>
       <c r="C53" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D53" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>255</v>
@@ -2463,7 +2449,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -2471,22 +2457,22 @@
         <v>105</v>
       </c>
       <c r="C54" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D54" t="s">
-        <v>115</v>
-      </c>
-      <c r="E54" t="s">
-        <v>257</v>
-      </c>
-      <c r="F54">
-        <v>4.0099999999999997E-2</v>
-      </c>
-      <c r="G54" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F54" s="3">
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -2494,82 +2480,91 @@
         <v>105</v>
       </c>
       <c r="C55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F55" s="3">
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A56" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C56" t="s">
+        <v>114</v>
+      </c>
+      <c r="D56" t="s">
+        <v>115</v>
+      </c>
+      <c r="E56" t="s">
+        <v>257</v>
+      </c>
+      <c r="F56">
+        <v>4.0099999999999997E-2</v>
+      </c>
+      <c r="G56" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A57" t="s">
+        <v>104</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57" t="s">
         <v>116</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D57" t="s">
         <v>117</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E57" t="s">
         <v>255</v>
       </c>
-      <c r="F55">
+      <c r="F57">
         <v>8.6900000000000005E-2</v>
       </c>
-      <c r="G55" t="s">
+      <c r="G57" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>118</v>
-      </c>
-      <c r="B56" t="s">
-        <v>50</v>
-      </c>
-      <c r="C56" t="s">
-        <v>119</v>
-      </c>
-      <c r="D56" t="s">
-        <v>120</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F56" s="3">
-        <v>0.99</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>118</v>
-      </c>
-      <c r="B57" t="s">
-        <v>121</v>
-      </c>
-      <c r="C57" t="s">
-        <v>122</v>
-      </c>
-      <c r="D57" t="s">
-        <v>123</v>
-      </c>
-      <c r="E57" t="s">
-        <v>261</v>
-      </c>
-      <c r="F57">
-        <v>0.88100000000000001</v>
-      </c>
-      <c r="G57" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>118</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="C58" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D58" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>118</v>
       </c>
@@ -2577,129 +2572,116 @@
         <v>121</v>
       </c>
       <c r="C59" t="s">
+        <v>122</v>
+      </c>
+      <c r="D59" t="s">
+        <v>123</v>
+      </c>
+      <c r="E59" t="s">
+        <v>261</v>
+      </c>
+      <c r="F59">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="G59" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A60" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="D60" t="s">
+        <v>125</v>
+      </c>
+      <c r="F60">
+        <v>1456.53</v>
+      </c>
+      <c r="G60" t="s">
+        <v>297</v>
+      </c>
+      <c r="L60" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A61" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" t="s">
+        <v>121</v>
+      </c>
+      <c r="C61" t="s">
         <v>126</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D61" t="s">
         <v>127</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E61" t="s">
         <v>207</v>
       </c>
-      <c r="F59">
+      <c r="F61">
         <v>8.3800000000000008</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G61" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E60" t="s">
-        <v>203</v>
-      </c>
-      <c r="F60">
-        <v>2.36</v>
-      </c>
-      <c r="G60" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="10"/>
-      <c r="B61" s="10"/>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" t="s">
-        <v>205</v>
-      </c>
-      <c r="F61">
-        <v>22.5</v>
-      </c>
-      <c r="G61" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>118</v>
       </c>
       <c r="B62" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C62" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D62" t="s">
-        <v>132</v>
-      </c>
-      <c r="E62" t="s">
-        <v>264</v>
+        <v>129</v>
       </c>
       <c r="F62">
-        <v>445</v>
-      </c>
-      <c r="G62" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>118</v>
-      </c>
-      <c r="B63" t="s">
-        <v>130</v>
-      </c>
-      <c r="C63" t="s">
-        <v>133</v>
-      </c>
-      <c r="D63" t="s">
-        <v>134</v>
-      </c>
+        <f>AVERAGE(F63:F64)</f>
+        <v>12.43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A63" s="10"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
       <c r="E63" t="s">
-        <v>265</v>
-      </c>
-      <c r="F63" s="6">
-        <v>35300</v>
+        <v>203</v>
+      </c>
+      <c r="F63">
+        <v>2.36</v>
       </c>
       <c r="G63" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>118</v>
-      </c>
-      <c r="B64" t="s">
-        <v>130</v>
-      </c>
-      <c r="C64" t="s">
-        <v>135</v>
-      </c>
-      <c r="D64" t="s">
-        <v>136</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F64" s="3">
-        <v>5.52</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A64" s="10"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" t="s">
+        <v>205</v>
+      </c>
+      <c r="F64">
+        <v>22.5</v>
+      </c>
+      <c r="G64" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A65" t="s">
         <v>118</v>
       </c>
@@ -2707,22 +2689,22 @@
         <v>130</v>
       </c>
       <c r="C65" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D65" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E65" t="s">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="F65">
-        <v>2.13</v>
+        <v>445</v>
       </c>
       <c r="G65" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -2730,22 +2712,22 @@
         <v>130</v>
       </c>
       <c r="C66" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D66" t="s">
-        <v>140</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F66" s="3">
-        <v>12.5</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="E66" t="s">
+        <v>265</v>
+      </c>
+      <c r="F66" s="6">
+        <v>35300</v>
+      </c>
+      <c r="G66" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>118</v>
       </c>
@@ -2753,22 +2735,22 @@
         <v>130</v>
       </c>
       <c r="C67" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D67" t="s">
-        <v>142</v>
-      </c>
-      <c r="E67" t="s">
-        <v>266</v>
-      </c>
-      <c r="F67">
-        <v>1.64</v>
-      </c>
-      <c r="G67" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F67" s="3">
+        <v>5.52</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
         <v>118</v>
       </c>
@@ -2776,22 +2758,22 @@
         <v>130</v>
       </c>
       <c r="C68" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D68" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E68" t="s">
-        <v>267</v>
-      </c>
-      <c r="F68" s="6">
-        <v>24900</v>
+        <v>194</v>
+      </c>
+      <c r="F68">
+        <v>2.13</v>
       </c>
       <c r="G68" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A69" t="s">
         <v>118</v>
       </c>
@@ -2799,22 +2781,22 @@
         <v>130</v>
       </c>
       <c r="C69" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D69" t="s">
-        <v>146</v>
-      </c>
-      <c r="E69" t="s">
-        <v>268</v>
-      </c>
-      <c r="F69" s="6">
-        <v>28100</v>
-      </c>
-      <c r="G69" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F69" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A70" t="s">
         <v>118</v>
       </c>
@@ -2822,22 +2804,22 @@
         <v>130</v>
       </c>
       <c r="C70" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D70" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E70" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F70">
-        <v>32.1</v>
+        <v>1.64</v>
       </c>
       <c r="G70" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
         <v>118</v>
       </c>
@@ -2845,22 +2827,22 @@
         <v>130</v>
       </c>
       <c r="C71" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D71" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E71" t="s">
-        <v>270</v>
-      </c>
-      <c r="F71">
-        <v>27</v>
+        <v>267</v>
+      </c>
+      <c r="F71" s="6">
+        <v>24900</v>
       </c>
       <c r="G71" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A72" t="s">
         <v>118</v>
       </c>
@@ -2868,22 +2850,22 @@
         <v>130</v>
       </c>
       <c r="C72" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D72" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E72" t="s">
-        <v>284</v>
-      </c>
-      <c r="F72">
-        <v>0.29399999999999998</v>
+        <v>268</v>
+      </c>
+      <c r="F72" s="6">
+        <v>28100</v>
       </c>
       <c r="G72" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A73" t="s">
         <v>118</v>
       </c>
@@ -2891,22 +2873,22 @@
         <v>130</v>
       </c>
       <c r="C73" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D73" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E73" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="F73">
-        <v>1.24</v>
+        <v>32.1</v>
       </c>
       <c r="G73" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A74" t="s">
         <v>118</v>
       </c>
@@ -2914,22 +2896,22 @@
         <v>130</v>
       </c>
       <c r="C74" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D74" t="s">
-        <v>156</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="F74" s="7">
-        <v>45</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="E74" t="s">
+        <v>270</v>
+      </c>
+      <c r="F74">
+        <v>27</v>
+      </c>
+      <c r="G74" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2937,22 +2919,22 @@
         <v>130</v>
       </c>
       <c r="C75" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D75" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E75" t="s">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="F75">
-        <v>16.7</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="G75" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A76" t="s">
         <v>118</v>
       </c>
@@ -2960,22 +2942,22 @@
         <v>130</v>
       </c>
       <c r="C76" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D76" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E76" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="F76">
-        <v>5.62</v>
+        <v>1.24</v>
       </c>
       <c r="G76" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A77" t="s">
         <v>118</v>
       </c>
@@ -2983,22 +2965,22 @@
         <v>130</v>
       </c>
       <c r="C77" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D77" t="s">
-        <v>162</v>
-      </c>
-      <c r="E77" t="s">
-        <v>273</v>
-      </c>
-      <c r="F77" s="6">
-        <v>118000</v>
-      </c>
-      <c r="G77" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F77" s="7">
+        <v>45</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A78" t="s">
         <v>118</v>
       </c>
@@ -3006,170 +2988,240 @@
         <v>130</v>
       </c>
       <c r="C78" t="s">
+        <v>157</v>
+      </c>
+      <c r="D78" t="s">
+        <v>158</v>
+      </c>
+      <c r="E78" t="s">
+        <v>249</v>
+      </c>
+      <c r="F78">
+        <v>16.7</v>
+      </c>
+      <c r="G78" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A79" t="s">
+        <v>118</v>
+      </c>
+      <c r="B79" t="s">
+        <v>130</v>
+      </c>
+      <c r="C79" t="s">
+        <v>159</v>
+      </c>
+      <c r="D79" t="s">
+        <v>160</v>
+      </c>
+      <c r="E79" t="s">
+        <v>272</v>
+      </c>
+      <c r="F79">
+        <v>5.62</v>
+      </c>
+      <c r="G79" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A80" t="s">
+        <v>118</v>
+      </c>
+      <c r="B80" t="s">
+        <v>130</v>
+      </c>
+      <c r="C80" t="s">
+        <v>161</v>
+      </c>
+      <c r="D80" t="s">
+        <v>162</v>
+      </c>
+      <c r="E80" t="s">
+        <v>273</v>
+      </c>
+      <c r="F80" s="6">
+        <v>118000</v>
+      </c>
+      <c r="G80" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.75">
+      <c r="A81" t="s">
+        <v>118</v>
+      </c>
+      <c r="B81" t="s">
+        <v>130</v>
+      </c>
+      <c r="C81" t="s">
         <v>163</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D81" t="s">
         <v>164</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E81" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F81" s="7">
         <f>107000*0.86</f>
         <v>92020</v>
       </c>
-      <c r="G78" s="7" t="s">
+      <c r="G81" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="Q78" t="s">
+      <c r="Q81" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.75">
+      <c r="A82" t="s">
         <v>118</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B82" t="s">
         <v>130</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C82" t="s">
         <v>165</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D82" t="s">
         <v>166</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E82" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F82" s="7">
         <f>10300*0.86</f>
         <v>8858</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="G82" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="Q79" t="s">
+      <c r="Q82" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.75">
+      <c r="A83" t="s">
         <v>118</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B83" t="s">
         <v>130</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C83" t="s">
         <v>167</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D83" t="s">
         <v>168</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E83" t="s">
         <v>290</v>
       </c>
-      <c r="F80">
+      <c r="F83">
         <v>49.5</v>
       </c>
-      <c r="G80" t="s">
+      <c r="G83" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>169</v>
-      </c>
-      <c r="B81" t="s">
-        <v>170</v>
-      </c>
-      <c r="C81" t="s">
-        <v>171</v>
-      </c>
-      <c r="D81" t="s">
-        <v>172</v>
-      </c>
-      <c r="G81" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>169</v>
-      </c>
-      <c r="B82" t="s">
-        <v>173</v>
-      </c>
-      <c r="C82" t="s">
-        <v>174</v>
-      </c>
-      <c r="D82" t="s">
-        <v>175</v>
-      </c>
-      <c r="G82" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>169</v>
-      </c>
-      <c r="B83" t="s">
-        <v>176</v>
-      </c>
-      <c r="C83" t="s">
-        <v>177</v>
-      </c>
-      <c r="D83" t="s">
-        <v>178</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="F83" s="8">
-        <f>AVERAGE(F78:F79,F68:F69,F77)</f>
-        <v>54375.6</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A84" t="s">
         <v>169</v>
       </c>
       <c r="B84" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D84" t="s">
+        <v>172</v>
+      </c>
+      <c r="F84">
+        <v>24609920</v>
+      </c>
+      <c r="G84" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.75">
+      <c r="A85" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" t="s">
+        <v>173</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D85" t="s">
+        <v>175</v>
+      </c>
+      <c r="E85" t="s">
+        <v>300</v>
+      </c>
+      <c r="F85">
+        <v>0.24</v>
+      </c>
+      <c r="G85" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.75">
+      <c r="A86" t="s">
+        <v>169</v>
+      </c>
+      <c r="B86" t="s">
+        <v>176</v>
+      </c>
+      <c r="C86" t="s">
+        <v>177</v>
+      </c>
+      <c r="D86" t="s">
+        <v>178</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F86" s="8">
+        <f>AVERAGE(F81:F82,F71:F72,F80)</f>
+        <v>54375.6</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.75">
+      <c r="A87" t="s">
+        <v>169</v>
+      </c>
+      <c r="B87" t="s">
         <v>179</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C87" t="s">
         <v>180</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D87" t="s">
         <v>181</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E87" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F87" s="3">
         <v>8.6900000000000005E-2</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="G87" s="3" t="s">
         <v>256</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
+  <mergeCells count="4">
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:D64"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{9B08079F-6631-49A5-8047-874B0E998448}"/>
@@ -3178,9 +3230,9 @@
     <hyperlink ref="G5" r:id="rId4" xr:uid="{C7F2CD44-015A-454D-BCA9-240DB7DDC922}"/>
     <hyperlink ref="G6" r:id="rId5" xr:uid="{80AC76BE-D6C1-494A-B6A4-50B84FF949CA}"/>
     <hyperlink ref="G10" r:id="rId6" xr:uid="{4DD938DE-8948-47A8-8630-85DF0C972A5C}"/>
-    <hyperlink ref="G44" r:id="rId7" xr:uid="{523F7310-806C-481A-85FF-51B7F8B8EAAB}"/>
+    <hyperlink ref="G46" r:id="rId7" xr:uid="{523F7310-806C-481A-85FF-51B7F8B8EAAB}"/>
     <hyperlink ref="G9" r:id="rId8" xr:uid="{FBACBB21-1F5D-43E9-901F-3651F9F72D65}"/>
-    <hyperlink ref="G74" r:id="rId9" location=":~:text=Currently%2C%20niobium%20prices%20range%20from,specialised%20products%20realise%20higher%20prices." xr:uid="{611CE029-EF7F-449F-AF7D-ADEC470297CE}"/>
+    <hyperlink ref="G77" r:id="rId9" location=":~:text=Currently%2C%20niobium%20prices%20range%20from,specialised%20products%20realise%20higher%20prices." xr:uid="{611CE029-EF7F-449F-AF7D-ADEC470297CE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/manual/materials_prices.xlsx
+++ b/data/manual/materials_prices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpsich-my.sharepoint.com/personal/alvaro_hahn-menacho_psi_ch/Documents/Severin's work/3_Code/semesterproject/data/manual/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ethz-my.sharepoint.com/personal/sewaelty_ethz_ch/Documents/Master Energy Science and Technology/S3/Semester Project/Project/3_Code/semesterproject/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="190" documentId="13_ncr:1_{D88AC83D-3D0E-48F6-B25A-3A931C8EAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BE5B1C7-5415-467C-BCA0-27A3ABC7A18A}"/>
+  <xr:revisionPtr revIDLastSave="197" documentId="13_ncr:1_{D88AC83D-3D0E-48F6-B25A-3A931C8EAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DFA854F-56A2-4435-8F05-AC1ACEAA6C46}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -893,9 +893,6 @@
     <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/20867/exchanges</t>
   </si>
   <si>
-    <t>https://www.globemm.com/niobium-markets#:~:text=Currently%2C%20niobium%20prices%20range%20from,specialised%20products%20realise%20higher%20prices.</t>
-  </si>
-  <si>
     <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/1387/exchanges</t>
   </si>
   <si>
@@ -939,6 +936,9 @@
   </si>
   <si>
     <t>https://ecoquery.ecoinvent.org/3.11/cutoff/dataset/19124/exchanges</t>
+  </si>
+  <si>
+    <t>https://www.scrapmonster.com/metal-prices/minor-metals/niobium/761</t>
   </si>
 </sst>
 </file>
@@ -970,7 +970,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -989,6 +989,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1003,7 +1009,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1016,12 +1022,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1328,17 +1333,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.54296875" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1361,7 +1366,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1383,8 +1388,9 @@
       <c r="G2" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N2" s="12"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1406,8 +1412,9 @@
       <c r="G3" s="2" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N3" s="12"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1429,8 +1436,9 @@
       <c r="G4" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N4" s="12"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1452,8 +1460,9 @@
       <c r="G5" s="2" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N5" s="12"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1475,8 +1484,9 @@
       <c r="G6" s="2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N6" s="12"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1490,16 +1500,17 @@
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F7">
         <v>5.84</v>
       </c>
       <c r="G7" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+        <v>292</v>
+      </c>
+      <c r="N7" s="12"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1515,8 +1526,9 @@
       <c r="H8" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N8" s="12"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1538,8 +1550,9 @@
       <c r="G9" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N9" s="12"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1561,28 +1574,29 @@
       <c r="G10" s="4" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A11" s="11" t="s">
+      <c r="N10" s="12"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12">
+      <c r="F11">
         <f>AVERAGE(F12:F13)</f>
         <v>1.1739999999999999</v>
       </c>
-      <c r="G11" s="13"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="G11" s="10"/>
+      <c r="N11" s="12"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
         <v>201</v>
       </c>
@@ -1592,12 +1606,9 @@
       <c r="G12" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+      <c r="N12" s="12"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
         <v>199</v>
       </c>
@@ -1607,8 +1618,9 @@
       <c r="G13" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N13" s="12"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1624,8 +1636,9 @@
       <c r="H14" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N14" s="12"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1647,8 +1660,9 @@
       <c r="G15" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N15" s="12"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1670,8 +1684,9 @@
       <c r="G16" s="3" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N16" s="12"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1693,8 +1708,9 @@
       <c r="G17" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N17" s="12"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1716,8 +1732,9 @@
       <c r="G18" s="3" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N18" s="12"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -1739,8 +1756,9 @@
       <c r="G19" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N19" s="12"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1756,8 +1774,9 @@
       <c r="H20" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N20" s="12"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1773,8 +1792,9 @@
       <c r="H21" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N21" s="12"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -1790,8 +1810,9 @@
       <c r="H22" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N22" s="12"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -1813,8 +1834,9 @@
       <c r="G23" s="3" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N23" s="12"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -1836,8 +1858,9 @@
       <c r="G24" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N24" s="12"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1859,8 +1882,9 @@
       <c r="G25" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N25" s="12"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -1882,8 +1906,9 @@
       <c r="G26" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N26" s="12"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1905,8 +1930,9 @@
       <c r="G27" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N27" s="12"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -1928,8 +1954,9 @@
       <c r="G28" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N28" s="12"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -1945,26 +1972,28 @@
       <c r="H29" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A30" s="11" t="s">
+      <c r="N29" s="12"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" t="s">
         <v>65</v>
       </c>
       <c r="F30">
         <f>AVERAGE(F31:F32)</f>
         <v>4.265E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N30" s="12"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E31" t="s">
         <v>230</v>
       </c>
@@ -1974,12 +2003,9 @@
       <c r="G31" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
+      <c r="N31" s="12"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E32" t="s">
         <v>231</v>
       </c>
@@ -1989,8 +2015,9 @@
       <c r="G32" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N32" s="12"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -2012,8 +2039,9 @@
       <c r="G33" s="3" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N33" s="12"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -2035,8 +2063,9 @@
       <c r="G34" s="3" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N34" s="12"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -2052,8 +2081,9 @@
       <c r="H35" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N35" s="12"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -2075,8 +2105,9 @@
       <c r="G36" s="3" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N36" s="12"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -2098,8 +2129,9 @@
       <c r="G37" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N37" s="12"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2121,8 +2153,9 @@
       <c r="G38" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N38" s="12"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -2144,8 +2177,9 @@
       <c r="G39" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N39" s="12"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -2167,8 +2201,9 @@
       <c r="G40" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N40" s="12"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>38</v>
       </c>
@@ -2190,8 +2225,9 @@
       <c r="G41" s="3" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N41" s="12"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>38</v>
       </c>
@@ -2213,8 +2249,9 @@
       <c r="G42" s="3" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N42" s="12"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -2236,8 +2273,9 @@
       <c r="G43" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N43" s="12"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -2253,8 +2291,9 @@
       <c r="H44" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N44" s="12"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -2276,8 +2315,9 @@
       <c r="G45" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N45" s="12"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -2299,8 +2339,9 @@
       <c r="G46" s="4" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N46" s="12"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>38</v>
       </c>
@@ -2322,8 +2363,9 @@
       <c r="G47" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="N47" s="12"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>38</v>
       </c>
@@ -2339,8 +2381,9 @@
       <c r="H48" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N48" s="12"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>38</v>
       </c>
@@ -2362,8 +2405,9 @@
       <c r="G49" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N49" s="12"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>38</v>
       </c>
@@ -2379,8 +2423,9 @@
       <c r="H50" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N50" s="12"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>38</v>
       </c>
@@ -2402,8 +2447,9 @@
       <c r="G51" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N51" s="12"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>104</v>
       </c>
@@ -2425,8 +2471,9 @@
       <c r="G52" s="3" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N52" s="12"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -2448,8 +2495,9 @@
       <c r="G53" s="3" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N53" s="12"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -2471,8 +2519,9 @@
       <c r="G54" s="3" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N54" s="12"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -2494,8 +2543,9 @@
       <c r="G55" s="3" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N55" s="12"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>104</v>
       </c>
@@ -2517,8 +2567,9 @@
       <c r="G56" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N56" s="12"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>104</v>
       </c>
@@ -2540,8 +2591,9 @@
       <c r="G57" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N57" s="12"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>118</v>
       </c>
@@ -2563,8 +2615,9 @@
       <c r="G58" s="3" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N58" s="12"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>118</v>
       </c>
@@ -2586,15 +2639,16 @@
       <c r="G59" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N59" s="12"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>118</v>
       </c>
       <c r="B60" t="s">
         <v>121</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" t="s">
         <v>124</v>
       </c>
       <c r="D60" t="s">
@@ -2603,14 +2657,14 @@
       <c r="F60">
         <v>1456.53</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G60" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="L60" t="s">
         <v>297</v>
       </c>
-      <c r="L60" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.75">
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>118</v>
       </c>
@@ -2632,8 +2686,9 @@
       <c r="G61" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="N61" s="12"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -2650,12 +2705,13 @@
         <f>AVERAGE(F63:F64)</f>
         <v>12.43</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.75">
-      <c r="A63" s="10"/>
-      <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
+      <c r="N62" s="12"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
       <c r="E63" t="s">
         <v>203</v>
       </c>
@@ -2665,12 +2721,13 @@
       <c r="G63" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.75">
-      <c r="A64" s="10"/>
-      <c r="B64" s="10"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
+      <c r="N63" s="12"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="11"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
       <c r="E64" t="s">
         <v>205</v>
       </c>
@@ -2680,8 +2737,9 @@
       <c r="G64" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N64" s="12"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>118</v>
       </c>
@@ -2703,8 +2761,9 @@
       <c r="G65" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N65" s="12"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -2726,8 +2785,9 @@
       <c r="G66" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N66" s="12"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>118</v>
       </c>
@@ -2749,8 +2809,9 @@
       <c r="G67" s="3" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N67" s="12"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>118</v>
       </c>
@@ -2772,8 +2833,9 @@
       <c r="G68" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N68" s="12"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>118</v>
       </c>
@@ -2795,8 +2857,9 @@
       <c r="G69" s="3" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N69" s="12"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>118</v>
       </c>
@@ -2818,8 +2881,9 @@
       <c r="G70" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N70" s="12"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>118</v>
       </c>
@@ -2841,8 +2905,9 @@
       <c r="G71" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N71" s="12"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>118</v>
       </c>
@@ -2864,8 +2929,9 @@
       <c r="G72" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N72" s="12"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>118</v>
       </c>
@@ -2887,8 +2953,9 @@
       <c r="G73" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N73" s="12"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>118</v>
       </c>
@@ -2910,8 +2977,9 @@
       <c r="G74" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N74" s="12"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2933,8 +3001,9 @@
       <c r="G75" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N75" s="12"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>118</v>
       </c>
@@ -2956,8 +3025,9 @@
       <c r="G76" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="N76" s="12"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>118</v>
       </c>
@@ -2974,13 +3044,13 @@
         <v>271</v>
       </c>
       <c r="F77" s="7">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.75">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>118</v>
       </c>
@@ -3000,10 +3070,11 @@
         <v>16.7</v>
       </c>
       <c r="G78" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.75">
+        <v>286</v>
+      </c>
+      <c r="N78" s="12"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>118</v>
       </c>
@@ -3023,10 +3094,11 @@
         <v>5.62</v>
       </c>
       <c r="G79" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.75">
+        <v>287</v>
+      </c>
+      <c r="N79" s="12"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>118</v>
       </c>
@@ -3046,10 +3118,11 @@
         <v>118000</v>
       </c>
       <c r="G80" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.75">
+        <v>288</v>
+      </c>
+      <c r="N80" s="12"/>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>118</v>
       </c>
@@ -3070,13 +3143,13 @@
         <v>92020</v>
       </c>
       <c r="G81" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q81" t="s">
         <v>294</v>
       </c>
-      <c r="Q81" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.75">
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>118</v>
       </c>
@@ -3097,13 +3170,13 @@
         <v>8858</v>
       </c>
       <c r="G82" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q82" t="s">
         <v>294</v>
       </c>
-      <c r="Q82" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.75">
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>118</v>
       </c>
@@ -3117,23 +3190,24 @@
         <v>168</v>
       </c>
       <c r="E83" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F83">
         <v>49.5</v>
       </c>
       <c r="G83" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.75">
+        <v>290</v>
+      </c>
+      <c r="N83" s="12"/>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>169</v>
       </c>
       <c r="B84" t="s">
         <v>170</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" t="s">
         <v>171</v>
       </c>
       <c r="D84" t="s">
@@ -3142,34 +3216,35 @@
       <c r="F84">
         <v>24609920</v>
       </c>
-      <c r="G84" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.75">
+      <c r="G84" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>169</v>
       </c>
       <c r="B85" t="s">
         <v>173</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" t="s">
         <v>174</v>
       </c>
       <c r="D85" t="s">
         <v>175</v>
       </c>
       <c r="E85" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F85">
         <v>0.24</v>
       </c>
       <c r="G85" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.75">
+        <v>300</v>
+      </c>
+      <c r="N85" s="12"/>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>169</v>
       </c>
@@ -3190,10 +3265,11 @@
         <v>54375.6</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.75">
+        <v>295</v>
+      </c>
+      <c r="N86" s="12"/>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>169</v>
       </c>
@@ -3215,6 +3291,7 @@
       <c r="G87" s="3" t="s">
         <v>256</v>
       </c>
+      <c r="N87" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3232,7 +3309,8 @@
     <hyperlink ref="G10" r:id="rId6" xr:uid="{4DD938DE-8948-47A8-8630-85DF0C972A5C}"/>
     <hyperlink ref="G46" r:id="rId7" xr:uid="{523F7310-806C-481A-85FF-51B7F8B8EAAB}"/>
     <hyperlink ref="G9" r:id="rId8" xr:uid="{FBACBB21-1F5D-43E9-901F-3651F9F72D65}"/>
-    <hyperlink ref="G77" r:id="rId9" location=":~:text=Currently%2C%20niobium%20prices%20range%20from,specialised%20products%20realise%20higher%20prices." xr:uid="{611CE029-EF7F-449F-AF7D-ADEC470297CE}"/>
+    <hyperlink ref="G60" r:id="rId9" xr:uid="{5CFAF788-1DC0-4541-AA69-55C02F8ADE90}"/>
+    <hyperlink ref="G84" r:id="rId10" xr:uid="{00340828-D7BE-4113-821D-708102CB3F1C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
